--- a/docs/EchoMind_Audit_2026-10-14_Project2/09_Test_Reports/EM26-34_Test_Execution_Register.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/09_Test_Reports/EM26-34_Test_Execution_Register.xlsx
@@ -2431,7 +2431,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Issued for approval</t>
+          <t>APPROVED — 2026-10-20 (AR-2026-007)</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Alexander Peter (EchoMind Project Lead) — to confirm</t>
+          <t>Alexander Peter (EchoMind Project Lead) — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth (QA / MR) — to confirm</t>
+          <t>Sheryl Nazareth (QA / MR) — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Anita Johan (Managing Director) — to confirm</t>
+          <t>Anita Johan (Managing Director) — 2026-10-20</t>
         </is>
       </c>
     </row>
